--- a/data/trans_dic/P37-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,71</t>
+          <t>2,07; 5,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,63</t>
+          <t>3,93; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,22</t>
+          <t>3,26; 7,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,57</t>
+          <t>1,29; 8,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,34</t>
+          <t>1,19; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,52</t>
+          <t>1,84; 5,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,99</t>
+          <t>2,32; 6,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 18,3</t>
+          <t>8,31; 18,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,32</t>
+          <t>2,06; 4,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,39</t>
+          <t>3,51; 6,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,07</t>
+          <t>3,23; 6,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,6</t>
+          <t>5,08; 11,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,37</t>
+          <t>3,16; 6,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,18</t>
+          <t>4,39; 8,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,02</t>
+          <t>2,61; 6,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,59</t>
+          <t>7,75; 15,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,67</t>
+          <t>2,42; 5,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,53</t>
+          <t>3,74; 7,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,19</t>
+          <t>2,84; 6,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 18,66</t>
+          <t>9,06; 18,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,47</t>
+          <t>3,13; 5,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,06</t>
+          <t>4,46; 7,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,5</t>
+          <t>3,14; 5,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 16,11</t>
+          <t>9,81; 16,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,55</t>
+          <t>3,73; 7,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,67</t>
+          <t>5,74; 9,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,27</t>
+          <t>1,65; 4,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,41</t>
+          <t>12,84; 19,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,51</t>
+          <t>4,63; 8,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,31</t>
+          <t>5,48; 9,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,76</t>
+          <t>4,74; 8,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 19,08</t>
+          <t>13,75; 19,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,42</t>
+          <t>4,64; 7,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,88</t>
+          <t>6,05; 8,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,8</t>
+          <t>3,46; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,23</t>
+          <t>13,97; 18,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,34</t>
+          <t>5,21; 10,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,33</t>
+          <t>6,45; 11,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,73</t>
+          <t>5,86; 10,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 21,36</t>
+          <t>6,47; 21,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,26</t>
+          <t>3,28; 7,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,88</t>
+          <t>5,04; 9,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,24</t>
+          <t>5,34; 9,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 24,32</t>
+          <t>18,11; 24,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,11</t>
+          <t>4,78; 7,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,71</t>
+          <t>6,26; 9,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,13</t>
+          <t>6,13; 9,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 21,84</t>
+          <t>10,84; 22,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,71; 22,64</t>
+          <t>14,94; 22,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,59; 23,28</t>
+          <t>15,92; 23,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,57; 23,27</t>
+          <t>15,29; 22,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,91; 41,0</t>
+          <t>33,02; 40,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 21,58</t>
+          <t>14,13; 21,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,41; 22,84</t>
+          <t>15,22; 23,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,44</t>
+          <t>13,45; 21,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,19; 40,43</t>
+          <t>34,18; 40,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 21,2</t>
+          <t>15,53; 20,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,13</t>
+          <t>16,74; 22,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 20,64</t>
+          <t>15,57; 20,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,45; 39,38</t>
+          <t>34,51; 39,07</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,59; 45,63</t>
+          <t>33,92; 45,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,94; 63,43</t>
+          <t>51,04; 62,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,41; 52,42</t>
+          <t>41,07; 52,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,37; 76,66</t>
+          <t>68,85; 76,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,22; 49,52</t>
+          <t>39,0; 49,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,39; 53,19</t>
+          <t>42,67; 52,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,28; 49,06</t>
+          <t>37,37; 47,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72,11; 92,74</t>
+          <t>72,2; 91,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,42; 45,77</t>
+          <t>38,53; 46,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,41; 56,3</t>
+          <t>48,45; 56,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,97; 48,81</t>
+          <t>41,23; 48,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,44; 88,41</t>
+          <t>72,51; 89,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,04; 73,87</t>
+          <t>61,75; 74,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,36; 74,54</t>
+          <t>62,61; 74,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,73; 71,97</t>
+          <t>61,75; 71,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84,81; 90,96</t>
+          <t>85,06; 91,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,17; 67,53</t>
+          <t>55,89; 66,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,43; 69,56</t>
+          <t>59,37; 69,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,57; 64,75</t>
+          <t>54,32; 65,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,27; 89,01</t>
+          <t>84,24; 88,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,0; 68,34</t>
+          <t>59,92; 68,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,35; 70,16</t>
+          <t>62,44; 70,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58,48; 66,7</t>
+          <t>58,64; 66,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,38; 88,97</t>
+          <t>85,47; 89,23</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,97</t>
+          <t>12,76; 14,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,13</t>
+          <t>16,42; 19,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,53; 17,12</t>
+          <t>14,64; 17,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,85</t>
+          <t>22,0; 31,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,08</t>
+          <t>14,63; 17,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,95; 19,61</t>
+          <t>16,97; 19,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,93; 18,62</t>
+          <t>16,03; 18,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,91; 50,92</t>
+          <t>34,77; 49,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,07; 15,81</t>
+          <t>14,03; 15,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,03; 18,89</t>
+          <t>16,91; 18,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 17,43</t>
+          <t>15,65; 17,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,79; 40,34</t>
+          <t>31,01; 40,25</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10226; 28141</t>
+          <t>10219; 28454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18081; 39015</t>
+          <t>17760; 39674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14061; 34500</t>
+          <t>13658; 31837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5438; 34262</t>
+          <t>5146; 34276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5588; 20263</t>
+          <t>5569; 19443</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7853; 23754</t>
+          <t>7900; 23272</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8664; 23687</t>
+          <t>9168; 25098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25509; 57325</t>
+          <t>26028; 57953</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20227; 41480</t>
+          <t>19771; 43360</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29785; 56372</t>
+          <t>31001; 57740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25678; 49481</t>
+          <t>26371; 51279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38387; 82756</t>
+          <t>36195; 78814</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23047; 46865</t>
+          <t>23271; 46433</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29170; 56236</t>
+          <t>30150; 56153</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15853; 35532</t>
+          <t>15385; 35717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32974; 66023</t>
+          <t>32843; 67554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15107; 35477</t>
+          <t>15164; 35548</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22207; 45938</t>
+          <t>22817; 45283</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15866; 34890</t>
+          <t>16032; 34986</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43907; 95426</t>
+          <t>46361; 96312</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43619; 74508</t>
+          <t>42534; 71901</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57572; 91566</t>
+          <t>57810; 92661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36327; 63444</t>
+          <t>36235; 63451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90847; 150611</t>
+          <t>91743; 151910</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25002; 48198</t>
+          <t>23797; 48904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37758; 65915</t>
+          <t>39108; 66170</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10755; 28546</t>
+          <t>11020; 27924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68778; 104086</t>
+          <t>68841; 102873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31147; 58609</t>
+          <t>31904; 58314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38407; 66145</t>
+          <t>38975; 68148</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30947; 57928</t>
+          <t>31381; 55991</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75226; 103520</t>
+          <t>74600; 103378</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62940; 98539</t>
+          <t>61555; 96705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83932; 123733</t>
+          <t>84284; 122074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46829; 77234</t>
+          <t>46018; 76768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150617; 196624</t>
+          <t>150690; 195116</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28330; 53658</t>
+          <t>27069; 52360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38386; 69501</t>
+          <t>39579; 68795</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37697; 69294</t>
+          <t>37835; 66789</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58440; 189629</t>
+          <t>57474; 192847</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18302; 37432</t>
+          <t>16930; 36617</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31460; 60800</t>
+          <t>30974; 59372</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33097; 59958</t>
+          <t>34637; 61152</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128171; 173263</t>
+          <t>129025; 173386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50459; 83964</t>
+          <t>49451; 82394</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77834; 119328</t>
+          <t>76919; 120566</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78403; 118184</t>
+          <t>79454; 118326</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>161953; 349465</t>
+          <t>173490; 352777</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56902; 87539</t>
+          <t>57791; 86268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>66808; 99728</t>
+          <t>68205; 101053</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74397; 111201</t>
+          <t>73082; 109371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184701; 230091</t>
+          <t>185336; 228572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56231; 87182</t>
+          <t>57085; 88087</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68993; 102279</t>
+          <t>68172; 103088</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67384; 101575</t>
+          <t>66833; 105428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>186522; 220551</t>
+          <t>186470; 220480</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123010; 167589</t>
+          <t>122776; 163212</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143868; 193922</t>
+          <t>146714; 193989</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151304; 201203</t>
+          <t>151785; 202965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>381336; 435909</t>
+          <t>381996; 432383</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100880; 133083</t>
+          <t>98930; 132815</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160889; 196496</t>
+          <t>158129; 195124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>138450; 175257</t>
+          <t>137304; 173886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255409; 282244</t>
+          <t>253496; 281510</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>134488; 169823</t>
+          <t>133731; 168815</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>150046; 188285</t>
+          <t>151035; 186923</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>144592; 185319</t>
+          <t>141188; 180066</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>438677; 564187</t>
+          <t>439235; 558263</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>243786; 290486</t>
+          <t>244513; 291984</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321368; 373699</t>
+          <t>321618; 373707</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>291760; 347571</t>
+          <t>293621; 346041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>707425; 863323</t>
+          <t>708131; 869278</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>130218; 155031</t>
+          <t>129604; 155416</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155178; 185466</t>
+          <t>155785; 184464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158636; 184966</t>
+          <t>158686; 183540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>239821; 257196</t>
+          <t>240525; 257544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>187540; 225493</t>
+          <t>186620; 223557</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>231186; 270586</t>
+          <t>230923; 270120</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>218366; 259104</t>
+          <t>217360; 260898</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>358834; 379041</t>
+          <t>358708; 378724</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>326264; 371624</t>
+          <t>325851; 370871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>397655; 447487</t>
+          <t>398258; 446970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>384336; 438311</t>
+          <t>385375; 438954</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>604973; 630468</t>
+          <t>605628; 632256</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>415220; 490166</t>
+          <t>417913; 490096</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>559635; 654722</t>
+          <t>561934; 651223</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>493254; 581097</t>
+          <t>496907; 576882</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>772581; 1102113</t>
+          <t>761251; 1094074</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>491392; 576847</t>
+          <t>494083; 574991</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>602855; 697599</t>
+          <t>603682; 697331</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>564712; 659929</t>
+          <t>568059; 664023</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1277459; 1863471</t>
+          <t>1272239; 1826627</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>936157; 1051755</t>
+          <t>933527; 1045896</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1188426; 1318334</t>
+          <t>1180465; 1318056</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1079768; 1209766</t>
+          <t>1085633; 1210414</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2191821; 2871650</t>
+          <t>2207379; 2865676</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P37-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37-Edad-trans_dic.xlsx
@@ -664,27 +664,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,77</t>
+          <t>2,15; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,77</t>
+          <t>4,02; 8,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,59</t>
+          <t>3,27; 7,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,57</t>
+          <t>1,36; 7,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,17</t>
+          <t>1,28; 4,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,41</t>
+          <t>1,88; 5,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,34</t>
+          <t>2,18; 5,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 18,5</t>
+          <t>8,19; 17,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,52</t>
+          <t>2,07; 4,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,54</t>
+          <t>3,25; 6,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,29</t>
+          <t>3,17; 6,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,05</t>
+          <t>5,02; 10,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,31</t>
+          <t>3,19; 6,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,17</t>
+          <t>4,43; 8,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,05</t>
+          <t>2,56; 6,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,95</t>
+          <t>8,03; 15,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,68</t>
+          <t>2,34; 5,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,42</t>
+          <t>3,72; 7,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,21</t>
+          <t>2,75; 5,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 18,83</t>
+          <t>12,8; 19,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,28</t>
+          <t>3,13; 5,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,14</t>
+          <t>4,5; 7,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,5</t>
+          <t>3,06; 5,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 16,25</t>
+          <t>11,28; 16,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,66</t>
+          <t>3,94; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,7</t>
+          <t>5,6; 9,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,17</t>
+          <t>1,54; 4,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,18</t>
+          <t>12,11; 18,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,47</t>
+          <t>4,81; 8,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,59</t>
+          <t>5,46; 9,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,47</t>
+          <t>4,76; 8,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 19,06</t>
+          <t>13,38; 18,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,29</t>
+          <t>4,72; 7,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,77</t>
+          <t>5,93; 8,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,77</t>
+          <t>3,41; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,09</t>
+          <t>13,4; 17,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 10,09</t>
+          <t>5,24; 10,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,21</t>
+          <t>6,25; 11,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,34</t>
+          <t>5,95; 10,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 21,72</t>
+          <t>17,45; 23,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,1</t>
+          <t>3,46; 7,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 9,65</t>
+          <t>5,3; 9,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,42</t>
+          <t>5,24; 9,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,33</t>
+          <t>20,17; 25,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,96</t>
+          <t>5,02; 7,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,81</t>
+          <t>6,3; 9,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,14</t>
+          <t>5,92; 8,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 22,04</t>
+          <t>19,67; 23,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,94; 22,31</t>
+          <t>14,85; 22,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,59</t>
+          <t>15,7; 23,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,29; 22,88</t>
+          <t>15,7; 23,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,02; 40,73</t>
+          <t>33,03; 40,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 21,8</t>
+          <t>14,11; 21,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,02</t>
+          <t>15,75; 23,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 21,22</t>
+          <t>13,52; 20,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,18; 40,41</t>
+          <t>34,42; 40,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,53; 20,64</t>
+          <t>15,11; 20,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,74; 22,14</t>
+          <t>16,69; 22,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,57; 20,82</t>
+          <t>15,38; 20,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,51; 39,07</t>
+          <t>34,44; 39,37</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,92; 45,54</t>
+          <t>34,43; 45,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,04; 62,99</t>
+          <t>51,81; 63,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,07; 52,01</t>
+          <t>41,69; 52,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68,85; 76,46</t>
+          <t>68,35; 75,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,0; 49,23</t>
+          <t>39,24; 49,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,67; 52,8</t>
+          <t>42,47; 52,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,37; 47,67</t>
+          <t>37,72; 48,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72,2; 91,76</t>
+          <t>70,93; 76,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,53; 46,01</t>
+          <t>38,45; 45,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,45; 56,3</t>
+          <t>48,41; 56,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,23; 48,6</t>
+          <t>41,15; 48,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,51; 89,02</t>
+          <t>70,6; 75,55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,75; 74,05</t>
+          <t>61,05; 73,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,61; 74,13</t>
+          <t>62,16; 75,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,75; 71,42</t>
+          <t>61,29; 72,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,06; 91,08</t>
+          <t>84,58; 91,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,89; 66,95</t>
+          <t>55,99; 67,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,37; 69,44</t>
+          <t>59,41; 69,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,32; 65,2</t>
+          <t>54,21; 65,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,24; 88,94</t>
+          <t>84,26; 88,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59,92; 68,2</t>
+          <t>59,38; 68,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,44; 70,08</t>
+          <t>62,45; 70,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58,64; 66,79</t>
+          <t>58,95; 66,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,47; 89,23</t>
+          <t>85,26; 89,01</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,97</t>
+          <t>12,72; 15,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,03</t>
+          <t>16,35; 19,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,64; 17,0</t>
+          <t>14,52; 16,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,0; 31,62</t>
+          <t>29,39; 32,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,03</t>
+          <t>14,51; 17,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,97; 19,6</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 18,73</t>
+          <t>15,94; 18,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,77; 49,92</t>
+          <t>34,72; 37,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,03; 15,72</t>
+          <t>14,02; 15,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,91; 18,89</t>
+          <t>17,03; 18,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,65; 17,44</t>
+          <t>15,68; 17,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,01; 40,25</t>
+          <t>32,54; 34,59</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>57240</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10219; 28454</t>
+          <t>10603; 26728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17760; 39674</t>
+          <t>18162; 40518</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13658; 31837</t>
+          <t>13708; 32621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5146; 34276</t>
+          <t>5535; 28784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5569; 19443</t>
+          <t>5956; 20801</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7900; 23272</t>
+          <t>8090; 24279</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9168; 25098</t>
+          <t>8617; 23506</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26028; 57953</t>
+          <t>29676; 63138</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19771; 43360</t>
+          <t>19907; 41769</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31001; 57740</t>
+          <t>28641; 55822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26371; 51279</t>
+          <t>25856; 50289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36195; 78814</t>
+          <t>38700; 82527</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>53102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>81360</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>134462</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23271; 46433</t>
+          <t>23459; 47599</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30150; 56153</t>
+          <t>30468; 55462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15385; 35717</t>
+          <t>15111; 36072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32843; 67554</t>
+          <t>38285; 72888</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15164; 35548</t>
+          <t>14630; 34868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22817; 45283</t>
+          <t>22719; 44629</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16032; 34986</t>
+          <t>15477; 33745</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46361; 96312</t>
+          <t>64148; 99708</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42534; 71901</t>
+          <t>42647; 74501</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57810; 92661</t>
+          <t>58412; 91175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36235; 63451</t>
+          <t>35343; 61607</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91743; 151910</t>
+          <t>110297; 164035</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88334</t>
+          <t>98500</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>191085</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23797; 48904</t>
+          <t>25157; 48600</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39108; 66170</t>
+          <t>38202; 66879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11020; 27924</t>
+          <t>10298; 29111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68841; 102873</t>
+          <t>75174; 112715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31904; 58314</t>
+          <t>33096; 59313</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38975; 68148</t>
+          <t>38825; 65944</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31381; 55991</t>
+          <t>31464; 58040</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74600; 103378</t>
+          <t>83225; 115831</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61555; 96705</t>
+          <t>62687; 99714</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84284; 122074</t>
+          <t>82657; 123857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46018; 76768</t>
+          <t>45415; 76780</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150690; 195116</t>
+          <t>166500; 217049</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131581</t>
+          <t>143148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>154476</t>
+          <t>166690</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>286057</t>
+          <t>309838</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27069; 52360</t>
+          <t>27218; 52977</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39579; 68795</t>
+          <t>38376; 68286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37835; 66789</t>
+          <t>38433; 67518</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57474; 192847</t>
+          <t>122239; 165071</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16930; 36617</t>
+          <t>17860; 37973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30974; 59372</t>
+          <t>32578; 60736</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34637; 61152</t>
+          <t>33986; 60204</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>129025; 173386</t>
+          <t>148558; 184305</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49451; 82394</t>
+          <t>51941; 81826</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76919; 120566</t>
+          <t>77373; 118741</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79454; 118326</t>
+          <t>76684; 116380</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>173490; 352777</t>
+          <t>282732; 339780</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206427</t>
+          <t>222872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>226887</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>408533</t>
+          <t>449759</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57791; 86268</t>
+          <t>57409; 88433</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68205; 101053</t>
+          <t>67245; 101410</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73082; 109371</t>
+          <t>75048; 110528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185336; 228572</t>
+          <t>201251; 245314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57085; 88087</t>
+          <t>57008; 88522</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68172; 103088</t>
+          <t>70546; 104611</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66833; 105428</t>
+          <t>67186; 103192</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>186470; 220480</t>
+          <t>209335; 244851</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>122776; 163212</t>
+          <t>119498; 163747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146714; 193989</t>
+          <t>146239; 193936</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151785; 202965</t>
+          <t>149957; 202101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>381996; 432383</t>
+          <t>419251; 479313</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269319</t>
+          <t>293850</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>500941</t>
+          <t>324215</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>770260</t>
+          <t>618065</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>98930; 132815</t>
+          <t>100433; 132348</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>158129; 195124</t>
+          <t>160497; 197425</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>137304; 173886</t>
+          <t>139374; 177114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253496; 281510</t>
+          <t>278223; 307951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>133731; 168815</t>
+          <t>134573; 169419</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>151035; 186923</t>
+          <t>150325; 187437</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>141188; 180066</t>
+          <t>142474; 182530</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>439235; 558263</t>
+          <t>311515; 337134</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>244513; 291984</t>
+          <t>244028; 291680</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321618; 373707</t>
+          <t>321351; 374707</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>293621; 346041</t>
+          <t>293018; 345352</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>708131; 869278</t>
+          <t>597411; 639320</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249273</t>
+          <t>273157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>369069</t>
+          <t>402882</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>618342</t>
+          <t>676039</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>129604; 155416</t>
+          <t>128141; 155103</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155785; 184464</t>
+          <t>154658; 187621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158686; 183540</t>
+          <t>157508; 185980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240525; 257544</t>
+          <t>262359; 282830</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>186620; 223557</t>
+          <t>186968; 225056</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>230923; 270120</t>
+          <t>231103; 270027</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>217360; 260898</t>
+          <t>216929; 261279</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>358708; 378724</t>
+          <t>391473; 412809</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>325851; 370871</t>
+          <t>322914; 370048</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>398258; 446970</t>
+          <t>398339; 448978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>385375; 438954</t>
+          <t>387414; 438425</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>605628; 632256</t>
+          <t>660631; 689660</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>417913; 490096</t>
+          <t>416507; 494851</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>561934; 651223</t>
+          <t>559303; 651651</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>496907; 576882</t>
+          <t>492829; 574832</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>761251; 1094074</t>
+          <t>1038257; 1148687</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>494083; 574991</t>
+          <t>490061; 578056</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>603682; 697331</t>
+          <t>601675; 696575</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>568059; 664023</t>
+          <t>564882; 667564</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1272239; 1826627</t>
+          <t>1296631; 1403302</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>933527; 1045896</t>
+          <t>932541; 1048028</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1180465; 1318056</t>
+          <t>1188590; 1322663</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1085633; 1210414</t>
+          <t>1088262; 1210238</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2207379; 2865676</t>
+          <t>2365011; 2513361</t>
         </is>
       </c>
     </row>
